--- a/public/exports-from-60-with-coowners/29188386.xlsx
+++ b/public/exports-from-60-with-coowners/29188386.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468820</t>
+          <t xml:space="preserve">311468821</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405990</t>
+          <t xml:space="preserve">311405994</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311416780</t>
+          <t xml:space="preserve">311468976</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469035</t>
+          <t xml:space="preserve">311469044</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29188386.xlsx
+++ b/public/exports-from-60-with-coowners/29188386.xlsx
@@ -3739,12 +3739,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468821</t>
+          <t xml:space="preserve">311468820</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M50" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29188386.xlsx
+++ b/public/exports-from-60-with-coowners/29188386.xlsx
@@ -3964,7 +3964,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311405994</t>
+          <t xml:space="preserve">311405990</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311468976</t>
+          <t xml:space="preserve">311416780</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311469044</t>
+          <t xml:space="preserve">311469035</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
